--- a/Experiment3/Workspace/Models/data/25/eHMI_T_results.xlsx
+++ b/Experiment3/Workspace/Models/data/25/eHMI_T_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,81 +772,81 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C17</t>
         </is>
       </c>
     </row>
@@ -855,19 +855,19 @@
         <v>5</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -876,17 +876,17 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C18</t>
         </is>
       </c>
     </row>
@@ -895,38 +895,38 @@
         <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
     </row>
@@ -935,198 +935,198 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="n">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C23</t>
         </is>
       </c>
     </row>
@@ -1135,38 +1135,38 @@
         <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C24</t>
         </is>
       </c>
     </row>
@@ -1178,35 +1178,35 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C4</t>
         </is>
       </c>
     </row>
@@ -1215,38 +1215,38 @@
         <v>6</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C5</t>
         </is>
       </c>
     </row>
@@ -1255,145 +1255,145 @@
         <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1402,89 +1402,9 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L24" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>7</v>
-      </c>
-      <c r="L26" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
